--- a/2026/CUBE/Phase 3/Cube_Phase3_CWS_User_Stories/Day2/Cube_Ph3_CWS_User_Stories_Day2.xlsx
+++ b/2026/CUBE/Phase 3/Cube_Phase3_CWS_User_Stories/Day2/Cube_Ph3_CWS_User_Stories_Day2.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\ZTERS_docs\2026\CUBE\Phase 3\Cube_Phase3_CWS_User_Stories\Day2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FB50C0-F552-4E1C-9FEE-CDACF203EC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +24,1346 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="444">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Parent Task</t>
+  </si>
+  <si>
+    <t>Task Name</t>
+  </si>
+  <si>
+    <t>User Story</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Acceptance Criteria</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Mockups</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Responsible</t>
+  </si>
+  <si>
+    <t>Core Platform</t>
+  </si>
+  <si>
+    <t>Functional Logic</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-001</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Reporting</t>
+  </si>
+  <si>
+    <t>Contract Management</t>
+  </si>
+  <si>
+    <t>Customer Contracts</t>
+  </si>
+  <si>
+    <t>Contract Reporting &amp; Dashboards</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want dashboards and reporting for contracts under the Customers module, so that I can track contract data effectively.</t>
+  </si>
+  <si>
+    <t>Contracts currently exist under the Customers module in QuickBase, and there is a need for improved reporting and dashboard visibility for contract-related data.</t>
+  </si>
+  <si>
+    <t>1. Contracts visible in dashboards 2. Reporting available 3. Filters by customer/site 4. Aggregated metrics 5. Export capability</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [0:09:00]</t>
+  </si>
+  <si>
+    <t>Customer-level contracts</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-002</t>
+  </si>
+  <si>
+    <t>Data Model</t>
+  </si>
+  <si>
+    <t>Contract Storage</t>
+  </si>
+  <si>
+    <t>Document Table</t>
+  </si>
+  <si>
+    <t>Store Contracts in Document Table</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want contracts to be stored within the document table, so that they are managed consistently with other documents.</t>
+  </si>
+  <si>
+    <t>Contracts are part of the document table, meaning they should follow the same storage and management structure as other documents in the system.</t>
+  </si>
+  <si>
+    <t>1. Contracts stored in document table 2. Linked to customer/site 3. Accessible via UI 4. Version control possible 5. Metadata included</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [0:14:15]</t>
+  </si>
+  <si>
+    <t>Data structure alignment</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-003</t>
+  </si>
+  <si>
+    <t>Contract Creation</t>
+  </si>
+  <si>
+    <t>Contract Fields</t>
+  </si>
+  <si>
+    <t>Add Contract Duration Field</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want to define a contract duration period, so that I know how long the contract will run after the start date.</t>
+  </si>
+  <si>
+    <t>When creating a contract, the system must include a period-based field that determines the duration of the contract relative to the start date.</t>
+  </si>
+  <si>
+    <t>1. Duration field exists 2. Linked to start date 3. Calculates end date 4. Editable 5. Visible in UI</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [0:16:00]</t>
+  </si>
+  <si>
+    <t>Time-based logic</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-004</t>
+  </si>
+  <si>
+    <t>UX/UI</t>
+  </si>
+  <si>
+    <t>Data Validation</t>
+  </si>
+  <si>
+    <t>Remove “Unspecified” Option</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want the “Unspecified” option removed from PI frequency in contracts, so that data remains meaningful.</t>
+  </si>
+  <si>
+    <t>The “Unspecified” option in the contract PI frequency tab should be removed to enforce proper data entry.</t>
+  </si>
+  <si>
+    <t>1. Option removed 2. Valid values enforced 3. No null/invalid entries 4. Validation errors shown 5. Required field</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [0:17:00]</t>
+  </si>
+  <si>
+    <t>Data quality improvement</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-005</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>Contract Lifecycle</t>
+  </si>
+  <si>
+    <t>Contract Actions</t>
+  </si>
+  <si>
+    <t>Inactivate Contracts</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want to inactivate a contract, so that it is no longer active without deleting it.</t>
+  </si>
+  <si>
+    <t>The system must allow contracts to be marked as inactive, preserving historical data while removing them from active workflows.</t>
+  </si>
+  <si>
+    <t>1. Inactivate option exists 2. Status updated 3. Contract preserved 4. Not used in workflows 5. Visible as inactive</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [0:26:20]</t>
+  </si>
+  <si>
+    <t>Soft deactivation</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-006</t>
+  </si>
+  <si>
+    <t>Automation</t>
+  </si>
+  <si>
+    <t>Notifications</t>
+  </si>
+  <si>
+    <t>Expiration Alerts</t>
+  </si>
+  <si>
+    <t>Contract Expiration Notifications</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want notifications when a contract is about to expire, so that I can take action in advance.</t>
+  </si>
+  <si>
+    <t>The system should generate alerts when contracts are nearing expiration (e.g., 7, 3, 1 days before).</t>
+  </si>
+  <si>
+    <t>1. Notifications triggered 2. Configurable intervals (7/3/1) 3. Delivered to user 4. Visible alerts 5. Linked to contract</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [0:27:20]</t>
+  </si>
+  <si>
+    <t>Time-based alerts</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-007</t>
+  </si>
+  <si>
+    <t>Visibility</t>
+  </si>
+  <si>
+    <t>Status Indicators</t>
+  </si>
+  <si>
+    <t>Highlight Expired Contracts</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want expired contracts to be clearly visible, so that I can identify them quickly.</t>
+  </si>
+  <si>
+    <t>Expired contracts should have a clear status or visual indicator and be easily identifiable within the system.</t>
+  </si>
+  <si>
+    <t>1. Expired status exists 2. Visual indicator shown 3. Filter available 4. Listed in UI 5. Included in dashboards</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [0:32:00]</t>
+  </si>
+  <si>
+    <t>Visibility improvement</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-008</t>
+  </si>
+  <si>
+    <t>Status Management</t>
+  </si>
+  <si>
+    <t>Contract Status</t>
+  </si>
+  <si>
+    <t>Add New Contract Status</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want new statuses for contracts, so that contract lifecycle stages are clearly represented.</t>
+  </si>
+  <si>
+    <t>The system should introduce new statuses related to contracts to better reflect their lifecycle.</t>
+  </si>
+  <si>
+    <t>1. New statuses available 2. Status selectable 3. Reflected in UI 4. Used in workflows 5. Filterable</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [0:35:00]</t>
+  </si>
+  <si>
+    <t>Lifecycle clarity</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-009</t>
+  </si>
+  <si>
+    <t>Dashboards</t>
+  </si>
+  <si>
+    <t>Contract Monitoring</t>
+  </si>
+  <si>
+    <t>Dashboard for Outdated Contracts</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want a dashboard showing outdated contracts, so that I can identify contracts needing attention.</t>
+  </si>
+  <si>
+    <t>The system should provide a dashboard specifically for outdated or expired contracts.</t>
+  </si>
+  <si>
+    <t>1. Dashboard exists 2. Contracts listed 3. Filters available 4. Updated in real time 5. Exportable</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [0:38:00]</t>
+  </si>
+  <si>
+    <t>Monitoring tool</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-010</t>
+  </si>
+  <si>
+    <t>Coverage Tracking</t>
+  </si>
+  <si>
+    <t>Missing Contracts</t>
+  </si>
+  <si>
+    <t>Dashboard for Missing Contracts</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want to see which customers or sites do not have contracts, so that I can address gaps.</t>
+  </si>
+  <si>
+    <t>The system must provide a dashboard identifying customers or sites without associated contracts.</t>
+  </si>
+  <si>
+    <t>1. Missing contracts listed 2. Filter by customer/site 3. Clear indicators 4. Actionable list 5. Export capability</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [0:39:00]</t>
+  </si>
+  <si>
+    <t>Gap visibility</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-011</t>
+  </si>
+  <si>
+    <t>Renewal Management</t>
+  </si>
+  <si>
+    <t>Auto-Renew</t>
+  </si>
+  <si>
+    <t>Identify Auto-Renew Contracts</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want to identify contracts that auto-renew, so that I can track renewals.</t>
+  </si>
+  <si>
+    <t>The system must provide a way to clearly identify which contracts are set to auto-renew.</t>
+  </si>
+  <si>
+    <t>1. Auto-renew flag exists 2. Visible in UI 3. Filterable 4. Used in workflows 5. Stored in DB</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [0:42:00]</t>
+  </si>
+  <si>
+    <t>Renewal tracking</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-012</t>
+  </si>
+  <si>
+    <t>Configure Auto-Renew Fields</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want to configure auto-renew fields, so that contracts renew correctly.</t>
+  </si>
+  <si>
+    <t>The system must allow users to define and manage fields related to contract auto-renew behavior.</t>
+  </si>
+  <si>
+    <t>1. Fields editable 2. Linked to contract 3. Validations exist 4. Used in logic 5. Persisted</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [0:46:00]</t>
+  </si>
+  <si>
+    <t>Config enhancement</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-013</t>
+  </si>
+  <si>
+    <t>Contract Terms</t>
+  </si>
+  <si>
+    <t>Cancellation</t>
+  </si>
+  <si>
+    <t>Add Cancellation Terms</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want to define cancellation terms in contracts, so that contract conditions are clear.</t>
+  </si>
+  <si>
+    <t>The system must support adding and managing cancellation terms within contracts.</t>
+  </si>
+  <si>
+    <t>1. Field exists 2. Editable 3. Stored with contract 4. Visible 5. Included in reports</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [0:49:30]</t>
+  </si>
+  <si>
+    <t>Legal clarity</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-014</t>
+  </si>
+  <si>
+    <t>Pricing</t>
+  </si>
+  <si>
+    <t>PI Management</t>
+  </si>
+  <si>
+    <t>View PI Impact on Revenue</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want to see how price increases affect revenue, so that I can understand financial impact.</t>
+  </si>
+  <si>
+    <t>The system must provide visibility into how price increases impact revenue for a customer or across multiple customers over time.</t>
+  </si>
+  <si>
+    <t>1. Revenue projection shown 2. Based on PI data 3. Multi-customer view 4. Time-based analysis 5. Clear visualization</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [1:13:12]</t>
+  </si>
+  <si>
+    <t>Financial insight</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-015</t>
+  </si>
+  <si>
+    <t>Workflow Automation</t>
+  </si>
+  <si>
+    <t>PI Workflow</t>
+  </si>
+  <si>
+    <t>Automate PI Workflows</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want price increase workflows automated, so that manual work is reduced.</t>
+  </si>
+  <si>
+    <t>The system should automate workflows related to price increases, including triggers and actions.</t>
+  </si>
+  <si>
+    <t>1. Automation exists 2. Trigger conditions defined 3. Tasks created 4. Notifications sent 5. Logs recorded</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [2:37:00]</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-016</t>
+  </si>
+  <si>
+    <t>Vendor PI</t>
+  </si>
+  <si>
+    <t>Tracking</t>
+  </si>
+  <si>
+    <t>Track Vendor Price Increases</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want to track vendor price increases, so that I can manage cost changes.</t>
+  </si>
+  <si>
+    <t>The system must provide a way to track vendor price increases explicitly.</t>
+  </si>
+  <si>
+    <t>1. Vendor PI recorded 2. Linked to vendor 3. Editable 4. Visible 5. Stored historically</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [2:46:00]</t>
+  </si>
+  <si>
+    <t>Critical requirement</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-017</t>
+  </si>
+  <si>
+    <t>PI Input</t>
+  </si>
+  <si>
+    <t>Manual Entry</t>
+  </si>
+  <si>
+    <t>Manual PI Entry Fields</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want to manually input PI period and percentage, so that I can control pricing changes.</t>
+  </si>
+  <si>
+    <t>The system must allow manual entry of price increase period and percentage.</t>
+  </si>
+  <si>
+    <t>1. Fields exist 2. Editable 3. Validations applied 4. Stored correctly 5. Reflected in calculations</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [2:56:00]</t>
+  </si>
+  <si>
+    <t>Manual override</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-018</t>
+  </si>
+  <si>
+    <t>Data Integrity</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>Required Fields</t>
+  </si>
+  <si>
+    <t>Enforce Review Field</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want the review field to be required, so that it is never left blank.</t>
+  </si>
+  <si>
+    <t>The system must enforce that the review field cannot be empty.</t>
+  </si>
+  <si>
+    <t>1. Field required 2. Validation error shown 3. Cannot save empty 4. UI indicator 5. Stored properly</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [1:21:20]</t>
+  </si>
+  <si>
+    <t>Data validation</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-019</t>
+  </si>
+  <si>
+    <t>PI Coverage</t>
+  </si>
+  <si>
+    <t>Default PI</t>
+  </si>
+  <si>
+    <t>Assign PI to New Customers</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want every new customer to have a PI record, so that no customer is missed.</t>
+  </si>
+  <si>
+    <t>The system must automatically associate a PI record when a new customer is created.</t>
+  </si>
+  <si>
+    <t>1. PI auto-created 2. Linked to customer 3. Mandatory 4. Visible 5. Editable</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [1:22:00]</t>
+  </si>
+  <si>
+    <t>Prevent gaps</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-020</t>
+  </si>
+  <si>
+    <t>Workflow Validation</t>
+  </si>
+  <si>
+    <t>Contract Review</t>
+  </si>
+  <si>
+    <t>Pre-Renewal</t>
+  </si>
+  <si>
+    <t>Review Contract Before Renewal</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want to review contracts before renewal, so that I can apply price increases.</t>
+  </si>
+  <si>
+    <t>The system should allow reviewing contracts prior to renewal to apply price increases if needed.</t>
+  </si>
+  <si>
+    <t>1. Review stage exists 2. Editable 3. Linked to renewal 4. PI applied 5. Workflow enforced</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [1:25:00]</t>
+  </si>
+  <si>
+    <t>Pre-renewal logic</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-021</t>
+  </si>
+  <si>
+    <t>Contract Organization</t>
+  </si>
+  <si>
+    <t>Future Planning</t>
+  </si>
+  <si>
+    <t>Segregate Contracts</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want contracts segregated for future use, so that they are organized properly.</t>
+  </si>
+  <si>
+    <t>The system should allow segregation of contracts as a future feature.</t>
+  </si>
+  <si>
+    <t>1. Segregation logic exists 2. Categories defined 3. UI support 4. Filterable 5. Extendable</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [1:28:00]</t>
+  </si>
+  <si>
+    <t>Future feature</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-022</t>
+  </si>
+  <si>
+    <t>Manual Handling</t>
+  </si>
+  <si>
+    <t>Manual PI for Review Frequency</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want PI frequency set to “review” to require manual handling, so that I control updates.</t>
+  </si>
+  <si>
+    <t>When PI frequency is set to review, the process becomes manual.</t>
+  </si>
+  <si>
+    <t>1. Manual mode triggered 2. No automation 3. Editable 4. Clear indicator 5. Stored correctly</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [1:41:55]</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-023</t>
+  </si>
+  <si>
+    <t>Billing</t>
+  </si>
+  <si>
+    <t>Opt-Out</t>
+  </si>
+  <si>
+    <t>Add Billing Opt-Out Options</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want opt-out options in billing, so that customers can be excluded when needed.</t>
+  </si>
+  <si>
+    <t>The system must include opt-out options within the billing information tab.</t>
+  </si>
+  <si>
+    <t>1. Opt-out field exists 2. Editable 3. Affects billing 4. Visible 5. Stored</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [3:00:00]</t>
+  </si>
+  <si>
+    <t>Billing control</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-024</t>
+  </si>
+  <si>
+    <t>Bulk Operations</t>
+  </si>
+  <si>
+    <t>Bulk Actions</t>
+  </si>
+  <si>
+    <t>Enable Bulk Actions</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want bulk actions, so that I can perform operations on multiple records at once.</t>
+  </si>
+  <si>
+    <t>The system must allow bulk actions across records.</t>
+  </si>
+  <si>
+    <t>1. Multi-select enabled 2. Bulk actions available 3. Confirmations required 4. Logs recorded 5. Performance optimized</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [3:08:00]</t>
+  </si>
+  <si>
+    <t>Efficiency</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-025</t>
+  </si>
+  <si>
+    <t>Data Integration</t>
+  </si>
+  <si>
+    <t>Import Tool</t>
+  </si>
+  <si>
+    <t>Data Upload</t>
+  </si>
+  <si>
+    <t>Bulk Import Customers &amp; Sites</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want to import customers and sites in bulk, so that I can create multiple records at once.</t>
+  </si>
+  <si>
+    <t>The system must provide an upload/import tool capable of creating multiple customers and sites simultaneously with defined minimum fields and parsing rules.</t>
+  </si>
+  <si>
+    <t>1. Upload tool exists 2. Minimum fields defined 3. Parsing supported 4. Bulk creation works 5. Error handling shown</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [3:26:00]</t>
+  </si>
+  <si>
+    <t>CRITICAL FEATURE</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-026</t>
+  </si>
+  <si>
+    <t>Bulk Import</t>
+  </si>
+  <si>
+    <t>Advanced Import</t>
+  </si>
+  <si>
+    <t>Single File Hierarchical Import</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want to import customers, sites, and products in one spreadsheet, so that I can create all related records in one process.</t>
+  </si>
+  <si>
+    <t>The transcript describes a desired capability to upload a single spreadsheet containing hierarchical data (customers → sites → grease traps) and have the system process and create all records accordingly.</t>
+  </si>
+  <si>
+    <t>1. Single file upload 2. Hierarchical parsing 3. Customer creation 4. Site creation 5. Product creation</t>
+  </si>
+  <si>
+    <t>Day 2, Part 2 [0:20 – 0:45]</t>
+  </si>
+  <si>
+    <t>Advanced import vision</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-027</t>
+  </si>
+  <si>
+    <t>Data Processing</t>
+  </si>
+  <si>
+    <t>Hierarchical Data Parsing</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want the system to process hierarchical relationships automatically, so that parent-child records are created correctly.</t>
+  </si>
+  <si>
+    <t>The system should process data in sequence (customers → sites → products) to ensure relational integrity during imports.</t>
+  </si>
+  <si>
+    <t>1. Parent-first parsing 2. Child linking 3. Relationship integrity 4. Sequential processing 5. Error handling</t>
+  </si>
+  <si>
+    <t>Day 2, Part 2 [0:45 – 1:14]</t>
+  </si>
+  <si>
+    <t>Backend logic</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-028</t>
+  </si>
+  <si>
+    <t>Import Usability</t>
+  </si>
+  <si>
+    <t>Templates</t>
+  </si>
+  <si>
+    <t>Generate Import Templates</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want to generate templates with required fields, so that I can prepare import files correctly.</t>
+  </si>
+  <si>
+    <t>The system should provide templates with required and contingent fields to simplify the import process and reduce errors.</t>
+  </si>
+  <si>
+    <t>1. Template downloadable 2. Required fields listed 3. Optional fields shown 4. Format validation 5. Easy to use</t>
+  </si>
+  <si>
+    <t>Day 2, Part 2 [1:25 – 1:52]</t>
+  </si>
+  <si>
+    <t>Improves usability</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-029</t>
+  </si>
+  <si>
+    <t>Import Validation</t>
+  </si>
+  <si>
+    <t>Field Mapping</t>
+  </si>
+  <si>
+    <t>Validate Import Fields</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want the system to validate import data, so that incorrect or incomplete data is prevented.</t>
+  </si>
+  <si>
+    <t>The system should validate field mappings and required fields during import to ensure data consistency.</t>
+  </si>
+  <si>
+    <t>1. Required field validation 2. Error messages 3. Prevent invalid import 4. Field mapping verification 5. Data consistency checks</t>
+  </si>
+  <si>
+    <t>Data quality</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-030</t>
+  </si>
+  <si>
+    <t>Import Process</t>
+  </si>
+  <si>
+    <t>Simplification</t>
+  </si>
+  <si>
+    <t>Improve Import Process vs QuickBase</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want a simpler import process than QuickBase, so that data uploads are less cumbersome.</t>
+  </si>
+  <si>
+    <t>The current QuickBase import process is described as complex and inefficient, requiring multiple steps and manual mapping of IDs.</t>
+  </si>
+  <si>
+    <t>1. Fewer steps 2. Reduced manual mapping 3. Faster process 4. Clear UI 5. Efficient workflow</t>
+  </si>
+  <si>
+    <t>Day 2, Part 2 [2:29 – 2:52]</t>
+  </si>
+  <si>
+    <t>Pain point</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-031</t>
+  </si>
+  <si>
+    <t>Ticket Creation</t>
+  </si>
+  <si>
+    <t>Automate Service Ticket Creation</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want service tickets to be created automatically based on criteria, so that recurring services are managed efficiently.</t>
+  </si>
+  <si>
+    <t>The system uses automated processes (cron + pipelines) to create service tickets based on defined criteria such as cycle dates and service readiness.</t>
+  </si>
+  <si>
+    <t>1. Criteria-based creation 2. Runs automatically 3. Linked to service cycle 4. Prevent invalid creation 5. Logged execution</t>
+  </si>
+  <si>
+    <t>Day 2, Part 2 [3:19 – 5:00]</t>
+  </si>
+  <si>
+    <t>Core automation</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-032</t>
+  </si>
+  <si>
+    <t>Line Items</t>
+  </si>
+  <si>
+    <t>Automate Line Item Creation</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want line items to be created automatically from service tickets, so that billing is generated correctly.</t>
+  </si>
+  <si>
+    <t>Line items are created automatically from service tickets based on mapping and criteria, ensuring billing consistency.</t>
+  </si>
+  <si>
+    <t>1. Auto creation 2. Based on ticket 3. Mapping fields 4. Multiple items supported 5. Accurate billing data</t>
+  </si>
+  <si>
+    <t>Day 2, Part 2 [5:00 – 7:00]</t>
+  </si>
+  <si>
+    <t>Billing dependency</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-033</t>
+  </si>
+  <si>
+    <t>Workflow Design</t>
+  </si>
+  <si>
+    <t>Data Handling</t>
+  </si>
+  <si>
+    <t>Duplicate Data for Stability</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want data duplication handled correctly, so that price changes do not affect historical records.</t>
+  </si>
+  <si>
+    <t>The system currently duplicates data across records (instead of referencing) to prevent retroactive changes impacting historical records.</t>
+  </si>
+  <si>
+    <t>1. Data copied correctly 2. Historical integrity maintained 3. No retroactive changes 4. Stored separately 5. Consistent values</t>
+  </si>
+  <si>
+    <t>Day 2, Part 2 [5:30 – 7:30]</t>
+  </si>
+  <si>
+    <t>Important design decision</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-034</t>
+  </si>
+  <si>
+    <t>Workflow Criteria</t>
+  </si>
+  <si>
+    <t>Define Ticket Creation Criteria</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want clear criteria for ticket creation, so that only valid tickets are generated.</t>
+  </si>
+  <si>
+    <t>Ticket creation depends on multiple criteria such as billing readiness, cycle dates, and service configurations.</t>
+  </si>
+  <si>
+    <t>1. Criteria defined 2. Validation checks 3. Prevent invalid tickets 4. Configurable 5. Visible logic</t>
+  </si>
+  <si>
+    <t>Criteria-driven</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-035</t>
+  </si>
+  <si>
+    <t>Scheduling</t>
+  </si>
+  <si>
+    <t>Cron Jobs</t>
+  </si>
+  <si>
+    <t>Support Scheduled Automation</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want scheduled automations (cron jobs), so that processes run automatically at defined times.</t>
+  </si>
+  <si>
+    <t>The system relies on scheduled processes (cron jobs) to run workflows such as ticket creation, billing, and imports in sequence.</t>
+  </si>
+  <si>
+    <t>1. Scheduling supported 2. Runs automatically 3. Configurable timing 4. Sequential execution 5. Logging</t>
+  </si>
+  <si>
+    <t>Day 2, Part 2 [7:00 – 9:00]</t>
+  </si>
+  <si>
+    <t>Core architecture</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-036</t>
+  </si>
+  <si>
+    <t>Integration</t>
+  </si>
+  <si>
+    <t>System Integration</t>
+  </si>
+  <si>
+    <t>Webhooks/API</t>
+  </si>
+  <si>
+    <t>Support API-Based Automations</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want the system to support API/webhook integrations, so that external systems can interact with workflows.</t>
+  </si>
+  <si>
+    <t>The system uses API calls and webhooks to trigger actions, update records, and integrate with external systems.</t>
+  </si>
+  <si>
+    <t>1. API support 2. Webhooks supported 3. Trigger events 4. Data exchange 5. Logging</t>
+  </si>
+  <si>
+    <t>Day 2, Part 2 [9:00 – 11:00]</t>
+  </si>
+  <si>
+    <t>Integration layer</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-037</t>
+  </si>
+  <si>
+    <t>Tasks</t>
+  </si>
+  <si>
+    <t>Task Management</t>
+  </si>
+  <si>
+    <t>Follow-Up</t>
+  </si>
+  <si>
+    <t>Auto Create Follow-Up Tasks</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want tasks to automatically create follow-up tasks, so that I can manage ongoing work.</t>
+  </si>
+  <si>
+    <t>The system allows creating a future task automatically based on a checkbox (“plan next task”), triggering a pipeline to generate a new task.</t>
+  </si>
+  <si>
+    <t>1. Checkbox triggers task 2. New task created 3. Fields copied 4. Linked tasks 5. Confirmation logged</t>
+  </si>
+  <si>
+    <t>Day 2, Part 2 [12:00 – 14:00]</t>
+  </si>
+  <si>
+    <t>Task chaining</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-038</t>
+  </si>
+  <si>
+    <t>Task Tracking</t>
+  </si>
+  <si>
+    <t>Logging</t>
+  </si>
+  <si>
+    <t>Log Task Creation Results</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want task creation to be logged, so that I can confirm it was successful.</t>
+  </si>
+  <si>
+    <t>The system updates the original task record to confirm that a follow-up task was created successfully.</t>
+  </si>
+  <si>
+    <t>1. Logging exists 2. Status updated 3. Visible confirmation 4. Linked records 5. Error handling</t>
+  </si>
+  <si>
+    <t>Logging mechanism</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-039</t>
+  </si>
+  <si>
+    <t>Automation Management</t>
+  </si>
+  <si>
+    <t>Cleanup</t>
+  </si>
+  <si>
+    <t>Manage Active Automations</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want to identify and manage only relevant automations, so that unnecessary processes are removed.</t>
+  </si>
+  <si>
+    <t>Not all automations need to be migrated; only relevant and active ones should be considered for the new system.</t>
+  </si>
+  <si>
+    <t>1. Active automations identified 2. Inactive ignored 3. Editable list 4. Managed centrally 5. Documented</t>
+  </si>
+  <si>
+    <t>Day 2, Part 2 [18:13 – 18:38]</t>
+  </si>
+  <si>
+    <t>Migration strategy</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-040</t>
+  </si>
+  <si>
+    <t>Documentation</t>
+  </si>
+  <si>
+    <t>Knowledge Management</t>
+  </si>
+  <si>
+    <t>Documentation Strategy</t>
+  </si>
+  <si>
+    <t>Document Automation Processes</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want automation processes documented conceptually, so that users understand system behavior.</t>
+  </si>
+  <si>
+    <t>Documentation should explain what processes happen (e.g., automated ticket creation) without exposing technical implementation details.</t>
+  </si>
+  <si>
+    <t>1. Conceptual documentation 2. User-friendly explanation 3. No code exposure 4. Internal vs external docs 5. Clear process flow</t>
+  </si>
+  <si>
+    <t>Day 2, Part 2 [33:18 – 34:37]</t>
+  </si>
+  <si>
+    <t>Documentation approach</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-041</t>
+  </si>
+  <si>
+    <t>Vendor Price Increase</t>
+  </si>
+  <si>
+    <t>Accept/Reject Vendor PI</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want to accept or reject vendor price increases, so that I can control which changes are applied.</t>
+  </si>
+  <si>
+    <t>The transcript mentions the process of accepting vendor price increases, implying a decision step that determines whether a PI is applied or not.</t>
+  </si>
+  <si>
+    <t>1. Accept option available 2. Reject option available 3. Status updated 4. Decision logged 5. Impacts pricing</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [2:42:00 – 2:46:00]</t>
+  </si>
+  <si>
+    <t>⚠️ Needs validation (approval flow not fully defined)</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-042</t>
+  </si>
+  <si>
+    <t>Price Increase Input</t>
+  </si>
+  <si>
+    <t>PI Creation</t>
+  </si>
+  <si>
+    <t>Define PI Creation Method</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want a defined method to create price increases without relying on a button, so that the workflow aligns with current processes.</t>
+  </si>
+  <si>
+    <t>The transcript explicitly states that users do not use a button to add price increases, implying a different method must be defined in the system.</t>
+  </si>
+  <si>
+    <t>1. No button required 2. Alternative input method 3. Consistent workflow 4. UI clarity 5. User-friendly</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [2:42:00]</t>
+  </si>
+  <si>
+    <t>⚠️ UX decision required</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-043</t>
+  </si>
+  <si>
+    <t>Price Increase Logic</t>
+  </si>
+  <si>
+    <t>PI Frequency</t>
+  </si>
+  <si>
+    <t>PI Formula &amp; Override</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want price increase frequency to be calculated automatically with an option to override it, so that I can balance automation with manual control.</t>
+  </si>
+  <si>
+    <t>The transcript references a formula-driven PI frequency along with override capability, indicating both automated and manual control are required.</t>
+  </si>
+  <si>
+    <t>1. Formula applied 2. Override option exists 3. Manual input allowed 4. Correct calculation 5. Stored properly</t>
+  </si>
+  <si>
+    <t>Day 2, Part 1 [2:34:00 – 2:37:00]</t>
+  </si>
+  <si>
+    <t>⚠️ Formula logic not fully defined</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-044</t>
+  </si>
+  <si>
+    <t>Automation Sequencing</t>
+  </si>
+  <si>
+    <t>Process Order</t>
+  </si>
+  <si>
+    <t>Sequential Automation Execution</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want automated processes to run in sequence (tickets → line items → billing), so that downstream processes only execute when prerequisites are complete.</t>
+  </si>
+  <si>
+    <t>The transcript clearly describes a sequential execution model using cron jobs where processes depend on the completion of previous steps.</t>
+  </si>
+  <si>
+    <t>1. Execution order enforced 2. Dependencies respected 3. No early execution 4. Logging exists 5. Errors handled</t>
+  </si>
+  <si>
+    <t>⚠️ Critical system behavior</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-045</t>
+  </si>
+  <si>
+    <t>Automation Control</t>
+  </si>
+  <si>
+    <t>Loop Prevention</t>
+  </si>
+  <si>
+    <t>Prevent Duplicate Execution</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want the system to prevent repeated or duplicate automation execution, so that records are not recreated incorrectly.</t>
+  </si>
+  <si>
+    <t>The transcript highlights the need to prevent loops and repeated execution of automations by using flags and conditions.</t>
+  </si>
+  <si>
+    <t>1. Loop prevention logic 2. Flags updated 3. No duplicate records 4. Conditions enforced 5. Logged actions</t>
+  </si>
+  <si>
+    <t>Day 2, Part 2 [12:00 – 18:00]</t>
+  </si>
+  <si>
+    <t>⚠️ Prevents system failure</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-046</t>
+  </si>
+  <si>
+    <t>Line Item Logic</t>
+  </si>
+  <si>
+    <t>Conditional Billing</t>
+  </si>
+  <si>
+    <t>Conditional Line Item Rules</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want line items to follow conditional rules (e.g., taxability, seasonal fees), so that billing reflects real-world scenarios.</t>
+  </si>
+  <si>
+    <t>The transcript explains different criteria for line items such as taxability rules by state and seasonal fees like winter service charges.</t>
+  </si>
+  <si>
+    <t>1. Conditional logic applied 2. State-based rules 3. Seasonal logic 4. Correct charges 5. Configurable</t>
+  </si>
+  <si>
+    <t>Day 2, Part 2 [7:00 – 12:00]</t>
+  </si>
+  <si>
+    <t>⚠️ Complex billing logic</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-047</t>
+  </si>
+  <si>
+    <t>Sales / Leads</t>
+  </si>
+  <si>
+    <t>Lead Assignment</t>
+  </si>
+  <si>
+    <t>Distribution Logic</t>
+  </si>
+  <si>
+    <t>Round Robin Assignment</t>
+  </si>
+  <si>
+    <t>As an Account Manager (AM), I want leads to be assigned using a round robin system, so that workload is distributed evenly among users.</t>
+  </si>
+  <si>
+    <t>The transcript describes a round robin assignment mechanism based on ranking and record IDs to distribute leads across users.</t>
+  </si>
+  <si>
+    <t>1. Rotation logic exists 2. Even distribution 3. Ranking applied 4. No duplication 5. Logged assignment</t>
+  </si>
+  <si>
+    <t>Day 2, Part 2 [18:13 – 23:00]</t>
+  </si>
+  <si>
+    <t>⚠️ Not yet defined for CUBE</t>
+  </si>
+  <si>
+    <t>CUBE-CWS-D2-048</t>
+  </si>
+  <si>
+    <t>Documentation Levels</t>
+  </si>
+  <si>
+    <t>Separate Documentation Types</t>
+  </si>
+  <si>
+    <t>As a Technical Writer, I want to separate technical and user-facing documentation, so that each audience receives appropriate detail.</t>
+  </si>
+  <si>
+    <t>The transcript explicitly discusses different documentation levels: detailed technical documentation for internal teams and simplified conceptual explanations for end users.</t>
+  </si>
+  <si>
+    <t>1. Separate documentation types 2. User-friendly docs 3. Technical detail available 4. Organized structure 5. Accessible content</t>
+  </si>
+  <si>
+    <t>⚠️ Documentation strategy</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +1371,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +1402,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +1708,1939 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" customWidth="1"/>
+    <col min="6" max="6" width="28.140625" customWidth="1"/>
+    <col min="7" max="7" width="49.5703125" customWidth="1"/>
+    <col min="8" max="8" width="64.5703125" customWidth="1"/>
+    <col min="9" max="9" width="44.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
+    <col min="11" max="11" width="19.28515625" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>